--- a/data/trans_dic/P1432-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1432-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,45</t>
+          <t>1,6; 3,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,56</t>
+          <t>0,83; 2,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,64</t>
+          <t>0,9; 2,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,35</t>
+          <t>2,39; 4,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,89</t>
+          <t>2,65; 4,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,91</t>
+          <t>2,29; 4,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,68</t>
+          <t>2,21; 3,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,5</t>
+          <t>2,03; 3,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,44</t>
+          <t>1,92; 3,54</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,68</t>
+          <t>0,15; 0,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,94</t>
+          <t>0,16; 1,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,98</t>
+          <t>0,25; 1,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,74</t>
+          <t>0,16; 0,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,26</t>
+          <t>0,45; 1,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,71</t>
+          <t>0,27; 0,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,69</t>
+          <t>0,23; 0,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,75</t>
+          <t>0,28; 0,75</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,19</t>
+          <t>0,29; 2,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,07</t>
+          <t>0,21; 2,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,14</t>
+          <t>0,1; 1,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,98</t>
+          <t>0,1; 0,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,88</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,51</t>
+          <t>0,8; 1,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,07</t>
+          <t>0,41; 1,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,8</t>
+          <t>0,34; 0,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,01</t>
+          <t>1,11; 1,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,16</t>
+          <t>1,22; 2,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,95</t>
+          <t>1,04; 1,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,6</t>
+          <t>1,03; 1,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,43</t>
+          <t>0,89; 1,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,28</t>
+          <t>0,77; 1,26</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16552; 35592</t>
+          <t>16504; 35397</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8007; 24944</t>
+          <t>8052; 25015</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6918; 19909</t>
+          <t>6826; 20113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30253; 57204</t>
+          <t>31383; 57229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36606; 65369</t>
+          <t>35452; 65134</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23406; 48795</t>
+          <t>22764; 47859</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52618; 86374</t>
+          <t>51760; 84690</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47523; 80952</t>
+          <t>46928; 80513</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32954; 60141</t>
+          <t>33570; 61997</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2514; 11488</t>
+          <t>2602; 12251</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4145; 18401</t>
+          <t>3168; 19612</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1690; 10418</t>
+          <t>1705; 10375</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3852; 15485</t>
+          <t>3898; 16459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2138; 13033</t>
+          <t>2854; 13147</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9158; 25022</t>
+          <t>8855; 24361</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8149; 23141</t>
+          <t>8724; 23205</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7897; 25665</t>
+          <t>8535; 25065</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12203; 30603</t>
+          <t>11424; 30376</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1018; 12052</t>
+          <t>1626; 12333</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4545</t>
+          <t>0; 5234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1652,27 +1652,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>981; 9487</t>
+          <t>974; 9227</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 8173</t>
+          <t>0; 8773</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1057; 11743</t>
+          <t>1010; 11344</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>976; 9170</t>
+          <t>973; 8481</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>889; 8405</t>
+          <t>898; 9619</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26480; 49392</t>
+          <t>26081; 49788</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14646; 36519</t>
+          <t>13923; 35122</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11057; 26907</t>
+          <t>11580; 26244</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38308; 68044</t>
+          <t>37609; 66395</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42621; 76667</t>
+          <t>43279; 74767</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37860; 68749</t>
+          <t>36674; 66829</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68992; 106354</t>
+          <t>68472; 106966</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64181; 99892</t>
+          <t>62086; 98397</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53577; 88753</t>
+          <t>53087; 86737</t>
         </is>
       </c>
     </row>
